--- a/research/traditional_assets/database/data/poland/poland_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_auto_truck.xlsx
@@ -587,26 +587,8 @@
           <t>Auto &amp; Truck</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.91</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
       <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+        <v>-0.023</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -614,12 +596,18 @@
       <c r="N2">
         <v>0</v>
       </c>
+      <c r="O2">
+        <v>-0</v>
+      </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
+      <c r="R2">
+        <v>-0</v>
+      </c>
       <c r="S2">
         <v>0</v>
       </c>
@@ -630,49 +618,49 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>-0.0471311475409836</v>
       </c>
       <c r="X2">
-        <v>0.07005043947935459</v>
+        <v>0.1166643227387248</v>
       </c>
       <c r="Y2">
-        <v>-0.07005043947935459</v>
+        <v>-0.1637954702797084</v>
       </c>
       <c r="Z2">
-        <v>0.1460055096418733</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.1460055096418733</v>
+        <v>-0.2614107883817428</v>
       </c>
       <c r="AB2">
-        <v>0.06900346099946371</v>
+        <v>0.1155958863263575</v>
       </c>
       <c r="AC2">
-        <v>0.0770020486424096</v>
+        <v>-0.3770066747081003</v>
       </c>
       <c r="AD2">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AG2">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AH2">
-        <v>0.02678571428571429</v>
+        <v>0.01761658031088083</v>
       </c>
       <c r="AI2">
-        <v>0.1448275862068966</v>
+        <v>0.1808510638297872</v>
       </c>
       <c r="AJ2">
-        <v>0.02678571428571429</v>
+        <v>0.01761658031088083</v>
       </c>
       <c r="AK2">
-        <v>0.1448275862068966</v>
+        <v>0.1808510638297872</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -689,7 +677,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arrinera S.A. (WSE:ARX)</t>
+          <t>Garin S.A. (WSE:ARX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -697,26 +685,8 @@
           <t>Auto &amp; Truck</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.91</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
       <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+        <v>-0.023</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -724,12 +694,18 @@
       <c r="N3">
         <v>-0</v>
       </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
       <c r="P3">
         <v>-0</v>
       </c>
       <c r="Q3">
         <v>-0</v>
       </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
       <c r="S3">
         <v>0</v>
       </c>
@@ -740,49 +716,49 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>-0.0471311475409836</v>
       </c>
       <c r="X3">
-        <v>0.07005043947935459</v>
+        <v>0.1166643227387248</v>
       </c>
       <c r="Y3">
-        <v>-0.07005043947935459</v>
+        <v>-0.1637954702797084</v>
       </c>
       <c r="Z3">
-        <v>0.1460055096418733</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.1460055096418733</v>
+        <v>-0.2614107883817428</v>
       </c>
       <c r="AB3">
-        <v>0.06900346099946371</v>
+        <v>0.1155958863263575</v>
       </c>
       <c r="AC3">
-        <v>0.0770020486424096</v>
+        <v>-0.3770066747081003</v>
       </c>
       <c r="AD3">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AG3">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AH3">
-        <v>0.02678571428571429</v>
+        <v>0.01761658031088083</v>
       </c>
       <c r="AI3">
-        <v>0.1448275862068966</v>
+        <v>0.1808510638297872</v>
       </c>
       <c r="AJ3">
-        <v>0.02678571428571429</v>
+        <v>0.01761658031088083</v>
       </c>
       <c r="AK3">
-        <v>0.1448275862068966</v>
+        <v>0.1808510638297872</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/poland/poland_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_auto_truck.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.023</v>
+        <v>-0.288</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,55 +612,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.00572737686139748</v>
       </c>
       <c r="W2">
-        <v>-0.0471311475409836</v>
+        <v>-3.74025974025974</v>
       </c>
       <c r="X2">
-        <v>0.1166643227387248</v>
+        <v>0.09912920439735497</v>
       </c>
       <c r="Y2">
-        <v>-0.1637954702797084</v>
+        <v>-3.839388944657095</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.2614107883817428</v>
+        <v>-0.1595744680851064</v>
       </c>
       <c r="AB2">
-        <v>0.1155958863263575</v>
+        <v>0.09810023939492653</v>
       </c>
       <c r="AC2">
-        <v>-0.3770066747081003</v>
+        <v>-0.2576747074800329</v>
       </c>
       <c r="AD2">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="AG2">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="AH2">
-        <v>0.01761658031088083</v>
+        <v>0.02130044843049327</v>
       </c>
       <c r="AI2">
-        <v>0.1808510638297872</v>
+        <v>0.2065217391304348</v>
       </c>
       <c r="AJ2">
-        <v>0.01761658031088083</v>
+        <v>0.01578354002254791</v>
       </c>
       <c r="AK2">
-        <v>0.1808510638297872</v>
+        <v>0.1609195402298851</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -677,7 +677,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Garin S.A. (WSE:ARX)</t>
+          <t>Garin S.A. (WSE:GAR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.023</v>
+        <v>-0.288</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -710,55 +710,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.00572737686139748</v>
       </c>
       <c r="W3">
-        <v>-0.0471311475409836</v>
+        <v>-3.74025974025974</v>
       </c>
       <c r="X3">
-        <v>0.1166643227387248</v>
+        <v>0.09912920439735497</v>
       </c>
       <c r="Y3">
-        <v>-0.1637954702797084</v>
+        <v>-3.839388944657095</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.2614107883817428</v>
+        <v>-0.1595744680851064</v>
       </c>
       <c r="AB3">
-        <v>0.1155958863263575</v>
+        <v>0.09810023939492653</v>
       </c>
       <c r="AC3">
-        <v>-0.3770066747081003</v>
+        <v>-0.2576747074800329</v>
       </c>
       <c r="AD3">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="AG3">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="AH3">
-        <v>0.01761658031088083</v>
+        <v>0.02130044843049327</v>
       </c>
       <c r="AI3">
-        <v>0.1808510638297872</v>
+        <v>0.2065217391304348</v>
       </c>
       <c r="AJ3">
-        <v>0.01761658031088083</v>
+        <v>0.01578354002254791</v>
       </c>
       <c r="AK3">
-        <v>0.1808510638297872</v>
+        <v>0.1609195402298851</v>
       </c>
       <c r="AL3">
         <v>0</v>
